--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00138_18940629.5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -963,7 +963,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00138_18940629.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y164"/>
+  <dimension ref="A1:Y180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L161: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: COâ€™S.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L134: isolated marker/symbol line :: 54</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>803</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -695,17 +699,17 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L50: suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c each—Perfect Goods.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L196: stray/suspicious non-ASCII glyph(s): U+606F CJK UNIFIED IDEOGRAPH-606F | isolated marker/symbol line :: 息</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -779,12 +783,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L393: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: alive and thatâ€™s all; Mr. Goold, a black-</t>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -802,13 +806,13 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -826,12 +830,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -850,14 +854,10 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Algomaâ€”Some</t>
-        </is>
-      </c>
+          <t>L504: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -873,13 +873,13 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
+          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -921,14 +921,10 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Hartley in a Most Revolting Lightâ€”The</t>
-        </is>
-      </c>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 6Oo (letter/digit mix) :: cott ； Mr. Robillard nearly 6Oo in Rus-</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -948,11 +944,7 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
-        </is>
-      </c>
+      <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -990,16 +982,8 @@
           <t>L58: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): MaceCottonTtibbed (odd internal casing) :: -----------or MaceCottonTtibbed Vests, with half sleeves, long sleeves, or without</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Attorney-Generalâ€™s Department, decided</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1057,16 +1041,8 @@
           <t>L59: suspicious token(s): 35c (letter/digit mix) :: sleeves at 35c each. Best value ever shown.</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: house is my own and I donâ€™t care";</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1076,7 +1052,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1124,16 +1100,8 @@
           <t>L62: suspicious token(s): 50c (letter/digit mix) :: value at 25, 40 and 50c per pair. - . * on</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wouldnâ€™t, and did not for about four</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1143,7 +1111,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1169,12 +1137,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1191,16 +1159,8 @@
           <t>L101: suspicious token(s): sick31 (letter/digit mix) :: him on the road before he got sick31</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00AF MACRON | isolated marker/symbol line :: æ�¯</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1210,7 +1170,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1241,7 +1201,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1255,19 +1215,11 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
-        </is>
-      </c>
+          <t>L331: suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-—</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1277,7 +1229,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1303,12 +1255,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1325,16 +1277,8 @@
           <t>L403: suspicious token(s): 35c (letter/digit mix) :: , __________________________________________35c ''~</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1344,7 +1288,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
+          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1389,19 +1333,11 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) :: â€”____________________=85c. â€” â€”________________</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L213: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
-        </is>
-      </c>
+          <t>L477: suspicious token(s): 85c (letter/digit mix) :: —____________________=85c. — —________________</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1411,13 +1347,13 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
+          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1442,7 +1378,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1459,16 +1395,8 @@
           <t>L526: suspicious token(s): XXXxXXXXXXXXXXXXXX (odd internal casing) :: XXXxXXXXXXXXXXXXXX</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L425: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 876 fringed in Haldimand, and Mr. Sennâ€™s</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1478,7 +1406,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
+          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1526,16 +1454,8 @@
           <t>L576: suspicious token(s): canidaton25 (letter/digit mix) :: the Come nd canidaton25</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nipissing ; Mr. Bronson and Mr. Oâ€™Keefe</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1545,7 +1465,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L305: isolated marker/symbol line :: 50</t>
+          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1593,16 +1513,8 @@
           <t>L590: suspicious token(s): theSpectator (odd internal casing) | likely joined words/missing space :: which, of theSpectator himself. Yours,</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L223: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) :: â€”____________________=85c. â€” â€”________________</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1612,7 +1524,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: 54</t>
+          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1660,26 +1572,18 @@
           <t>L647: suspicious token(s): ladies1 (letter/digit mix) :: We will make it interesting for the ladies1</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦Â·.</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: canvassersâ€™ reports when men vote under</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L161: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L161: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L308: isolated marker/symbol line :: 46</t>
+          <t>L305: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1715,16 +1619,8 @@
           <t>L655: suspicious token(s): 124c (letter/digit mix) :: at 3 for 124c, will be continued this week. This/</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦Â·.</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: most of Adamâ€™sdescendants, they base</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1734,7 +1630,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L309: symbol-only separator/garbage line :: . 67</t>
+          <t>L307: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1770,16 +1666,8 @@
           <t>L656: suspicious token(s): 10c (letter/digit mix) :: marvelous bargain. They are worth 10c</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: she said if I wouldnâ€™t she would have</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1789,7 +1677,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L310: symbol-only separator/garbage line :: .125</t>
+          <t>L308: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1825,26 +1713,18 @@
           <t>L669: suspicious token(s): 123c (letter/digit mix) :: ful goods, 10 and 123c each, extra quality at 15</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to Quiggâ€™s, and the boys got beer and</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L167: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L311: symbol-only separator/garbage line :: .123</t>
+          <t>L309: symbol-only separator/garbage line :: . 67</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1877,29 +1757,21 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: can take it out inâ€™that way"; it was</t>
-        </is>
-      </c>
+          <t>L670: suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladies’ Balbriggan Vests. Men 8</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L168: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L312: symbol-only separator/garbage line :: .80</t>
+          <t>L310: symbol-only separator/garbage line :: .125</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1935,26 +1807,18 @@
           <t>L678: suspicious token(s): Stripe1Bathing (letter/digit mix) :: selling off at big reductions. Stripe1Bathing</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: each. Finch Bros.â€™ is the house for these goods.</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: Â·.</t>
+          <t>L169: isolated marker/symbol line :: ·.</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L313: symbol-only separator/garbage line :: .90</t>
+          <t>L311: symbol-only separator/garbage line :: .123</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1990,26 +1854,18 @@
           <t>L679: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix) :: Flannels 39c, worth 65c. Plain French Twill</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L660: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: seasonâ€™s, but we have made deep cuts in the</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L170: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L314: symbol-only separator/garbage line :: .40</t>
+          <t>L312: symbol-only separator/garbage line :: .80</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2045,16 +1901,8 @@
           <t>L680: suspicious token(s): 25c (letter/digit mix), 40c (letter/digit mix) :: Bathing Flannel 25c, worth 40c. Childrens</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2064,7 +1912,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 44</t>
+          <t>L313: symbol-only separator/garbage line :: .90</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2097,19 +1945,11 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Drawers. Ladiesâ€™ and Men's Hostery. Child-</t>
-        </is>
-      </c>
+          <t>L684: suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blouses—40c, for 29c; 50c, for 39c; 75c,</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2119,7 +1959,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: 77</t>
+          <t>L314: symbol-only separator/garbage line :: .40</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2155,16 +1995,8 @@
           <t>L685: suspicious token(s): 50c (letter/digit mix), 40c (letter/digit mix), 25c (letter/digit mix), 50c (letter/digit mix) :: for 50c. White Lawn Blouses 40c, for 25c. 50c</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2174,7 +2006,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L322: isolated marker/symbol line :: 13</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2210,16 +2042,8 @@
           <t>L686: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix), 49c (letter/digit mix), 70c (letter/digit mix), 59c (letter/digit mix) :: - Blouses 39c. 65c Blouses 49c. 70c Blouses 59c.</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at the house at 4 oâ€™clock ; when I got</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2229,7 +2053,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L324: isolated marker/symbol line :: 41</t>
+          <t>L318: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2265,16 +2089,8 @@
           <t>L703: suspicious token(s): 25c (letter/digit mix), 22c (letter/digit mix) :: extra large, 3 for 25c and 2 for 22c. Beach</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2284,7 +2100,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: 16</t>
+          <t>L320: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2320,16 +2136,8 @@
           <t>L736: suspicious token(s): 25c (letter/digit mix) :: Fine Dress Sateens 20 and 25c, nowselling off</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BERTRAMâ€™S</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2339,7 +2147,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L327: symbol-only separator/garbage line :: 21%</t>
+          <t>L322: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2375,26 +2183,18 @@
           <t>L738: suspicious token(s): 15c (letter/digit mix) :: 15c. all new styles. Handsome Broche Sateens</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: toriousâ€”being mistaken or classed together</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L186: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L329: symbol-only separator/garbage line :: 631 284</t>
+          <t>L324: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2427,29 +2227,21 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L824: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: with _. but weâ€™ve said enough on this subject</t>
-        </is>
-      </c>
+          <t>L839: suspicious token(s): 33Women’s (letter/digit mix) :: Our $1.33Women’s Strapor Tie Slippers we can</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L187: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L326: isolated marker/symbol line :: 16</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2477,7 +2269,7 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>L571: suspicious token(s): 6Oo (letter/digit mix) :: cott ï¼› Mr. Robillard nearly 6Oo in Rus-</t>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 6Oo (letter/digit mix) :: cott ； Mr. Robillard nearly 6Oo in Rus-</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
@@ -2485,16 +2277,8 @@
           <t>L847: suspicious token(s): Our32 (letter/digit mix) :: Our32.25 Men's Laced or Congress Boots we</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2504,7 +2288,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
+          <t>L327: symbol-only separator/garbage line :: 21%</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2540,16 +2324,8 @@
           <t>L946: punctuation artifact: repeated exclamation marks | suspicious token(s): PUI0 (letter/digit mix) :: KIIW an Ma PUI0 ua!!!!setive A . aO</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.35 Womenâ€™s Dongola Oxford Tie Shoes</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2559,7 +2335,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
+          <t>L329: symbol-only separator/garbage line :: 631 284</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2591,26 +2367,18 @@
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L299: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our 83 75 Menâ€™s Shell Cordovan Congress and</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2642,26 +2410,18 @@
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L850: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.75 Menâ€™s Laced Boots wo can prove to</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L193: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2693,16 +2453,8 @@
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: in Fred coming home, he couldnâ€™t do</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2712,7 +2464,7 @@
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
+          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2744,16 +2496,8 @@
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L997: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Branch Office, 31 King west, â€˜Phone 978</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2763,7 +2507,7 @@
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 57</t>
+          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2791,26 +2535,18 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L303: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L1054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and gentsâ€™, smoking</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00AF MACRON | isolated marker/symbol line :: æ�¯</t>
+          <t>L196: stray/suspicious non-ASCII glyph(s): U+606F CJK UNIFIED IDEOGRAPH-606F | isolated marker/symbol line :: 息</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: 29</t>
+          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2838,16 +2574,8 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦.</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L1060: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ADVERTISE IN THE TIMESâ€”</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
@@ -2857,7 +2585,7 @@
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: 12</t>
+          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2885,16 +2613,8 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L1062: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2904,7 +2624,7 @@
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 46</t>
+          <t>L351: isolated marker/symbol line :: 57</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2932,22 +2652,18 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L201: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L359: isolated marker/symbol line :: 47</t>
+          <t>L353: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2975,11 +2691,7 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
@@ -2990,13 +2702,13 @@
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: 51</t>
+          <t>L355: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
+          <t>L763: punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a d— of</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -3018,11 +2730,7 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L328: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
@@ -3033,7 +2741,7 @@
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 242</t>
+          <t>L357: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3061,11 +2769,7 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
@@ -3076,7 +2780,7 @@
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
+          <t>L359: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3100,11 +2804,7 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
@@ -3115,7 +2815,7 @@
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L367: symbol-only separator/garbage line :: .....30</t>
+          <t>L361: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3139,11 +2839,7 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
@@ -3154,7 +2850,7 @@
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L369: symbol-only separator/garbage line :: .....46</t>
+          <t>L363: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3178,22 +2874,18 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L210: isolated marker/symbol line :: Â·.</t>
+          <t>L210: isolated marker/symbol line :: ·.</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L371: symbol-only separator/garbage line :: .....56</t>
+          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -3217,11 +2909,7 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
@@ -3232,7 +2920,7 @@
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: .....34</t>
+          <t>L367: symbol-only separator/garbage line :: .....30</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3256,22 +2944,18 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L212: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
+          <t>L369: symbol-only separator/garbage line :: .....46</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3295,22 +2979,18 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L214: isolated marker/symbol line :: 34</t>
+          <t>L213: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L377: isolated marker/symbol line :: 250</t>
+          <t>L371: symbol-only separator/garbage line :: .....56</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -3334,22 +3014,18 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L215: isolated marker/symbol line :: 47</t>
+          <t>L214: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: $1.75</t>
+          <t>L373: symbol-only separator/garbage line :: .....34</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3373,22 +3049,18 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L218: isolated marker/symbol line :: .</t>
+          <t>L215: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
+          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3412,22 +3084,18 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L219: isolated marker/symbol line :: .</t>
+          <t>L218: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
+          <t>L377: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3451,22 +3119,18 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L220: isolated marker/symbol line :: Â·</t>
+          <t>L219: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
+          <t>L385: symbol-only separator/garbage line :: $1.75</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
@@ -3490,22 +3154,18 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L220: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: 67</t>
+          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3529,22 +3189,18 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L224: isolated marker/symbol line :: .</t>
+          <t>L221: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: 78</t>
+          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3568,22 +3224,18 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L225: isolated marker/symbol line :: 35</t>
+          <t>L222: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L399: isolated marker/symbol line :: 54</t>
+          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3607,22 +3259,18 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L226: isolated marker/symbol line :: 51</t>
+          <t>L223: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: 199</t>
+          <t>L395: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3646,22 +3294,18 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L224: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: a</t>
+          <t>L397: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3685,22 +3329,18 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L225: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
+          <t>L399: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3724,22 +3364,18 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L365: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L226: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L405: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3763,22 +3399,18 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L235: isolated marker/symbol line :: .</t>
+          <t>L230: isolated marker/symbol line :: …·.</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
+          <t>L406: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3802,22 +3434,18 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L236: isolated marker/symbol line :: .</t>
+          <t>L231: isolated marker/symbol line :: …·.</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L411: isolated marker/symbol line :: 195</t>
+          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3841,22 +3469,18 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L238: isolated marker/symbol line :: 3</t>
+          <t>L232: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
+          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3880,22 +3504,18 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L240: isolated marker/symbol line :: 250</t>
+          <t>L233: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
+          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3919,22 +3539,18 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L370: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L241: isolated marker/symbol line :: 242</t>
+          <t>L234: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
+          <t>L411: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -3958,22 +3574,18 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L371: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L243: symbol-only separator/garbage line :: $1.75</t>
+          <t>L235: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 44</t>
+          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -3997,22 +3609,18 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L249: isolated marker/symbol line :: .</t>
+          <t>L236: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 58</t>
+          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4036,22 +3644,18 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L238: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 82</t>
+          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4075,22 +3679,18 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L240: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L469: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4114,22 +3714,18 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L241: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
+          <t>L470: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4153,22 +3749,18 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L253: isolated marker/symbol line :: 07</t>
+          <t>L243: symbol-only separator/garbage line :: $1.75</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
+          <t>L472: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4192,22 +3784,18 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L254: isolated marker/symbol line :: 52</t>
+          <t>L249: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
+          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4231,22 +3819,18 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L255: isolated marker/symbol line :: 67</t>
+          <t>L250: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
+          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4270,22 +3854,18 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L395: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L259: isolated marker/symbol line :: 123</t>
+          <t>L251: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 92</t>
+          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4309,22 +3889,18 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L396: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦ 1, 551</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: .</t>
+          <t>L252: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: 95</t>
+          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4348,22 +3924,18 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L667: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: said it's a h â€”- of a note or a d â€”â€” of</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L261: isolated marker/symbol line :: .</t>
+          <t>L253: isolated marker/symbol line :: 07</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: 84</t>
+          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4387,22 +3959,18 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: toriousâ€”being mi mistaken or classed together</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L254: isolated marker/symbol line :: 52</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 44</t>
+          <t>L491: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4426,22 +3994,18 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L879: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gentsâ€™Blouses,</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L255: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L499: isolated marker/symbol line :: 61</t>
+          <t>L493: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4471,12 +4035,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L259: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
+          <t>L495: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4506,12 +4070,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L265: isolated marker/symbol line :: 54</t>
+          <t>L260: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L503: isolated marker/symbol line :: 51</t>
+          <t>L497: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4541,12 +4105,12 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L266: isolated marker/symbol line :: 78</t>
+          <t>L261: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
+          <t>L499: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
@@ -4576,12 +4140,12 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L267: isolated marker/symbol line :: 45</t>
+          <t>L262: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
+          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
@@ -4611,12 +4175,12 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L271: isolated marker/symbol line :: .</t>
+          <t>L263: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
+          <t>L503: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
@@ -4646,12 +4210,12 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L272: isolated marker/symbol line :: 0.</t>
+          <t>L264: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
@@ -4681,12 +4245,12 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L265: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L518: isolated marker/symbol line :: 276</t>
+          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
@@ -4716,12 +4280,12 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L266: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
@@ -4751,10 +4315,14 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L278: isolated marker/symbol line :: 199</t>
-        </is>
-      </c>
-      <c r="O88" s="1" t="inlineStr"/>
+          <t>L267: isolated marker/symbol line :: 45</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="inlineStr">
+        <is>
+          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr"/>
       <c r="R88" s="1" t="inlineStr"/>
@@ -4782,10 +4350,14 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L279: isolated marker/symbol line :: 164</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr"/>
+          <t>L271: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="inlineStr">
+        <is>
+          <t>L518: isolated marker/symbol line :: 276</t>
+        </is>
+      </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr"/>
       <c r="R89" s="1" t="inlineStr"/>
@@ -4813,10 +4385,14 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L284: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O90" s="1" t="inlineStr"/>
+          <t>L272: isolated marker/symbol line :: 0.</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="inlineStr">
+        <is>
+          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+        </is>
+      </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr"/>
       <c r="R90" s="1" t="inlineStr"/>
@@ -4844,10 +4420,14 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L288: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O91" s="1" t="inlineStr"/>
+          <t>L273: isolated marker/symbol line :: ·…</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="inlineStr">
+        <is>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
+        </is>
+      </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr"/>
       <c r="R91" s="1" t="inlineStr"/>
@@ -4875,7 +4455,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L289: isolated marker/symbol line :: 00</t>
+          <t>L274: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4906,7 +4486,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L275: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4937,7 +4517,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L278: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4968,7 +4548,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L293: isolated marker/symbol line :: 63</t>
+          <t>L279: isolated marker/symbol line :: 164</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4999,7 +4579,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L294: isolated marker/symbol line :: 44</t>
+          <t>L284: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5030,7 +4610,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L295: isolated marker/symbol line :: 58</t>
+          <t>L288: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5061,7 +4641,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: 12</t>
+          <t>L289: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5092,7 +4672,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L299: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L290: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5123,7 +4703,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L291: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5154,7 +4734,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L292: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5185,7 +4765,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L293: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5216,7 +4796,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L303: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L294: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5247,7 +4827,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L304: isolated marker/symbol line :: 61</t>
+          <t>L295: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5278,7 +4858,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L305: isolated marker/symbol line :: 71</t>
+          <t>L298: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5309,7 +4889,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L306: isolated marker/symbol line :: 82</t>
+          <t>L299: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5340,7 +4920,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L311: isolated marker/symbol line :: .</t>
+          <t>L300: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5371,7 +4951,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L301: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5402,7 +4982,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L302: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5433,7 +5013,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L303: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5464,7 +5044,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 195</t>
+          <t>L304: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5495,7 +5075,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L319: isolated marker/symbol line :: 184</t>
+          <t>L305: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5526,7 +5106,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L327: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L306: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5557,7 +5137,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L310: isolated marker/symbol line :: .….</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5588,7 +5168,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L311: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5619,7 +5199,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L312: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5650,7 +5230,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L332: isolated marker/symbol line :: 73</t>
+          <t>L313: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5681,7 +5261,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L333: isolated marker/symbol line :: 95</t>
+          <t>L314: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5712,7 +5292,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: 92</t>
+          <t>L318: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5743,7 +5323,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L319: isolated marker/symbol line :: 184</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5774,7 +5354,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L327: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5805,7 +5385,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L328: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5836,7 +5416,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L329: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5867,7 +5447,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L330: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5898,7 +5478,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: 29</t>
+          <t>L331: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5929,7 +5509,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L346: isolated marker/symbol line :: 51</t>
+          <t>L332: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -5960,7 +5540,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L347: isolated marker/symbol line :: 84</t>
+          <t>L333: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -5991,7 +5571,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L351: symbol-only separator/garbage line :: 12845</t>
+          <t>L334: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6022,7 +5602,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L352: isolated marker/symbol line :: .</t>
+          <t>L338: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6053,7 +5633,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: .</t>
+          <t>L339: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6084,7 +5664,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L340: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6115,7 +5695,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L341: isolated marker/symbol line :: ……</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6146,7 +5726,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L342: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6177,7 +5757,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L358: isolated marker/symbol line :: 59</t>
+          <t>L343: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6208,7 +5788,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L359: isolated marker/symbol line :: 4</t>
+          <t>L344: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6239,7 +5819,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L345: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6270,7 +5850,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L346: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6301,7 +5881,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L365: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L347: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6332,7 +5912,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L351: symbol-only separator/garbage line :: 12845</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6363,7 +5943,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L352: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6394,7 +5974,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L353: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6425,7 +6005,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L354: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6456,7 +6036,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L370: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L355: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6487,7 +6067,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L371: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L356: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6518,7 +6098,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L357: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6549,7 +6129,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L358: isolated marker/symbol line :: 59</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6580,7 +6160,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L374: isolated marker/symbol line :: 64</t>
+          <t>L359: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6611,7 +6191,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L375: isolated marker/symbol line :: 61</t>
+          <t>L362: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6642,7 +6222,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L363: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6673,7 +6253,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L364: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6704,7 +6284,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L365: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6735,7 +6315,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L366: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6766,7 +6346,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L385: isolated marker/symbol line :: 276</t>
+          <t>L367: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -6797,7 +6377,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L386: isolated marker/symbol line :: 376</t>
+          <t>L368: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -6828,7 +6408,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L388: symbol-only separator/garbage line :: $2.00</t>
+          <t>L369: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -6859,7 +6439,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: ?</t>
+          <t>L370: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -6890,7 +6470,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L371: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -6921,7 +6501,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L395: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L372: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -6952,7 +6532,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L397: symbol-only separator/garbage line :: 1, 250</t>
+          <t>L373: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -6983,7 +6563,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L432: isolated marker/symbol line :: -</t>
+          <t>L374: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -7014,7 +6594,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L444: isolated marker/symbol line :: 3</t>
+          <t>L375: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -7045,7 +6625,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L771: symbol-only separator/garbage line :: $1.50.</t>
+          <t>L379: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7076,7 +6656,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L853: isolated marker/symbol line :: `</t>
+          <t>L380: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7107,7 +6687,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L900: isolated marker/symbol line :: d</t>
+          <t>L381: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7122,6 +6702,502 @@
       <c r="X164" s="1" t="inlineStr"/>
       <c r="Y164" s="1" t="inlineStr"/>
     </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr"/>
+      <c r="B165" s="1" t="inlineStr"/>
+      <c r="C165" s="1" t="inlineStr"/>
+      <c r="D165" s="1" t="inlineStr"/>
+      <c r="E165" s="1" t="inlineStr"/>
+      <c r="F165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr"/>
+      <c r="H165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr"/>
+      <c r="J165" s="1" t="inlineStr"/>
+      <c r="K165" s="1" t="inlineStr"/>
+      <c r="L165" s="1" t="inlineStr"/>
+      <c r="M165" s="1" t="inlineStr"/>
+      <c r="N165" s="1" t="inlineStr">
+        <is>
+          <t>L382: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O165" s="1" t="inlineStr"/>
+      <c r="P165" s="1" t="inlineStr"/>
+      <c r="Q165" s="1" t="inlineStr"/>
+      <c r="R165" s="1" t="inlineStr"/>
+      <c r="S165" s="1" t="inlineStr"/>
+      <c r="T165" s="1" t="inlineStr"/>
+      <c r="U165" s="1" t="inlineStr"/>
+      <c r="V165" s="1" t="inlineStr"/>
+      <c r="W165" s="1" t="inlineStr"/>
+      <c r="X165" s="1" t="inlineStr"/>
+      <c r="Y165" s="1" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr"/>
+      <c r="B166" s="1" t="inlineStr"/>
+      <c r="C166" s="1" t="inlineStr"/>
+      <c r="D166" s="1" t="inlineStr"/>
+      <c r="E166" s="1" t="inlineStr"/>
+      <c r="F166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr"/>
+      <c r="H166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr"/>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
+      <c r="L166" s="1" t="inlineStr"/>
+      <c r="M166" s="1" t="inlineStr"/>
+      <c r="N166" s="1" t="inlineStr">
+        <is>
+          <t>L385: isolated marker/symbol line :: 276</t>
+        </is>
+      </c>
+      <c r="O166" s="1" t="inlineStr"/>
+      <c r="P166" s="1" t="inlineStr"/>
+      <c r="Q166" s="1" t="inlineStr"/>
+      <c r="R166" s="1" t="inlineStr"/>
+      <c r="S166" s="1" t="inlineStr"/>
+      <c r="T166" s="1" t="inlineStr"/>
+      <c r="U166" s="1" t="inlineStr"/>
+      <c r="V166" s="1" t="inlineStr"/>
+      <c r="W166" s="1" t="inlineStr"/>
+      <c r="X166" s="1" t="inlineStr"/>
+      <c r="Y166" s="1" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr"/>
+      <c r="B167" s="1" t="inlineStr"/>
+      <c r="C167" s="1" t="inlineStr"/>
+      <c r="D167" s="1" t="inlineStr"/>
+      <c r="E167" s="1" t="inlineStr"/>
+      <c r="F167" s="1" t="inlineStr"/>
+      <c r="G167" s="1" t="inlineStr"/>
+      <c r="H167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr"/>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
+      <c r="L167" s="1" t="inlineStr"/>
+      <c r="M167" s="1" t="inlineStr"/>
+      <c r="N167" s="1" t="inlineStr">
+        <is>
+          <t>L386: isolated marker/symbol line :: 376</t>
+        </is>
+      </c>
+      <c r="O167" s="1" t="inlineStr"/>
+      <c r="P167" s="1" t="inlineStr"/>
+      <c r="Q167" s="1" t="inlineStr"/>
+      <c r="R167" s="1" t="inlineStr"/>
+      <c r="S167" s="1" t="inlineStr"/>
+      <c r="T167" s="1" t="inlineStr"/>
+      <c r="U167" s="1" t="inlineStr"/>
+      <c r="V167" s="1" t="inlineStr"/>
+      <c r="W167" s="1" t="inlineStr"/>
+      <c r="X167" s="1" t="inlineStr"/>
+      <c r="Y167" s="1" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr"/>
+      <c r="B168" s="1" t="inlineStr"/>
+      <c r="C168" s="1" t="inlineStr"/>
+      <c r="D168" s="1" t="inlineStr"/>
+      <c r="E168" s="1" t="inlineStr"/>
+      <c r="F168" s="1" t="inlineStr"/>
+      <c r="G168" s="1" t="inlineStr"/>
+      <c r="H168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr"/>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
+      <c r="L168" s="1" t="inlineStr"/>
+      <c r="M168" s="1" t="inlineStr"/>
+      <c r="N168" s="1" t="inlineStr">
+        <is>
+          <t>L388: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
+      <c r="O168" s="1" t="inlineStr"/>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr"/>
+      <c r="R168" s="1" t="inlineStr"/>
+      <c r="S168" s="1" t="inlineStr"/>
+      <c r="T168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="inlineStr"/>
+      <c r="V168" s="1" t="inlineStr"/>
+      <c r="W168" s="1" t="inlineStr"/>
+      <c r="X168" s="1" t="inlineStr"/>
+      <c r="Y168" s="1" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr"/>
+      <c r="B169" s="1" t="inlineStr"/>
+      <c r="C169" s="1" t="inlineStr"/>
+      <c r="D169" s="1" t="inlineStr"/>
+      <c r="E169" s="1" t="inlineStr"/>
+      <c r="F169" s="1" t="inlineStr"/>
+      <c r="G169" s="1" t="inlineStr"/>
+      <c r="H169" s="1" t="inlineStr"/>
+      <c r="I169" s="1" t="inlineStr"/>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
+      <c r="L169" s="1" t="inlineStr"/>
+      <c r="M169" s="1" t="inlineStr"/>
+      <c r="N169" s="1" t="inlineStr">
+        <is>
+          <t>L392: isolated marker/symbol line :: ?</t>
+        </is>
+      </c>
+      <c r="O169" s="1" t="inlineStr"/>
+      <c r="P169" s="1" t="inlineStr"/>
+      <c r="Q169" s="1" t="inlineStr"/>
+      <c r="R169" s="1" t="inlineStr"/>
+      <c r="S169" s="1" t="inlineStr"/>
+      <c r="T169" s="1" t="inlineStr"/>
+      <c r="U169" s="1" t="inlineStr"/>
+      <c r="V169" s="1" t="inlineStr"/>
+      <c r="W169" s="1" t="inlineStr"/>
+      <c r="X169" s="1" t="inlineStr"/>
+      <c r="Y169" s="1" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr"/>
+      <c r="B170" s="1" t="inlineStr"/>
+      <c r="C170" s="1" t="inlineStr"/>
+      <c r="D170" s="1" t="inlineStr"/>
+      <c r="E170" s="1" t="inlineStr"/>
+      <c r="F170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr"/>
+      <c r="H170" s="1" t="inlineStr"/>
+      <c r="I170" s="1" t="inlineStr"/>
+      <c r="J170" s="1" t="inlineStr"/>
+      <c r="K170" s="1" t="inlineStr"/>
+      <c r="L170" s="1" t="inlineStr"/>
+      <c r="M170" s="1" t="inlineStr"/>
+      <c r="N170" s="1" t="inlineStr">
+        <is>
+          <t>L393: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O170" s="1" t="inlineStr"/>
+      <c r="P170" s="1" t="inlineStr"/>
+      <c r="Q170" s="1" t="inlineStr"/>
+      <c r="R170" s="1" t="inlineStr"/>
+      <c r="S170" s="1" t="inlineStr"/>
+      <c r="T170" s="1" t="inlineStr"/>
+      <c r="U170" s="1" t="inlineStr"/>
+      <c r="V170" s="1" t="inlineStr"/>
+      <c r="W170" s="1" t="inlineStr"/>
+      <c r="X170" s="1" t="inlineStr"/>
+      <c r="Y170" s="1" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr"/>
+      <c r="B171" s="1" t="inlineStr"/>
+      <c r="C171" s="1" t="inlineStr"/>
+      <c r="D171" s="1" t="inlineStr"/>
+      <c r="E171" s="1" t="inlineStr"/>
+      <c r="F171" s="1" t="inlineStr"/>
+      <c r="G171" s="1" t="inlineStr"/>
+      <c r="H171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr"/>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
+      <c r="L171" s="1" t="inlineStr"/>
+      <c r="M171" s="1" t="inlineStr"/>
+      <c r="N171" s="1" t="inlineStr">
+        <is>
+          <t>L394: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr"/>
+      <c r="R171" s="1" t="inlineStr"/>
+      <c r="S171" s="1" t="inlineStr"/>
+      <c r="T171" s="1" t="inlineStr"/>
+      <c r="U171" s="1" t="inlineStr"/>
+      <c r="V171" s="1" t="inlineStr"/>
+      <c r="W171" s="1" t="inlineStr"/>
+      <c r="X171" s="1" t="inlineStr"/>
+      <c r="Y171" s="1" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr"/>
+      <c r="B172" s="1" t="inlineStr"/>
+      <c r="C172" s="1" t="inlineStr"/>
+      <c r="D172" s="1" t="inlineStr"/>
+      <c r="E172" s="1" t="inlineStr"/>
+      <c r="F172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr"/>
+      <c r="H172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr"/>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
+      <c r="L172" s="1" t="inlineStr"/>
+      <c r="M172" s="1" t="inlineStr"/>
+      <c r="N172" s="1" t="inlineStr">
+        <is>
+          <t>L395: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr"/>
+      <c r="R172" s="1" t="inlineStr"/>
+      <c r="S172" s="1" t="inlineStr"/>
+      <c r="T172" s="1" t="inlineStr"/>
+      <c r="U172" s="1" t="inlineStr"/>
+      <c r="V172" s="1" t="inlineStr"/>
+      <c r="W172" s="1" t="inlineStr"/>
+      <c r="X172" s="1" t="inlineStr"/>
+      <c r="Y172" s="1" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr"/>
+      <c r="B173" s="1" t="inlineStr"/>
+      <c r="C173" s="1" t="inlineStr"/>
+      <c r="D173" s="1" t="inlineStr"/>
+      <c r="E173" s="1" t="inlineStr"/>
+      <c r="F173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr"/>
+      <c r="H173" s="1" t="inlineStr"/>
+      <c r="I173" s="1" t="inlineStr"/>
+      <c r="J173" s="1" t="inlineStr"/>
+      <c r="K173" s="1" t="inlineStr"/>
+      <c r="L173" s="1" t="inlineStr"/>
+      <c r="M173" s="1" t="inlineStr"/>
+      <c r="N173" s="1" t="inlineStr">
+        <is>
+          <t>L396: symbol-only separator/garbage line :: … 1, 551</t>
+        </is>
+      </c>
+      <c r="O173" s="1" t="inlineStr"/>
+      <c r="P173" s="1" t="inlineStr"/>
+      <c r="Q173" s="1" t="inlineStr"/>
+      <c r="R173" s="1" t="inlineStr"/>
+      <c r="S173" s="1" t="inlineStr"/>
+      <c r="T173" s="1" t="inlineStr"/>
+      <c r="U173" s="1" t="inlineStr"/>
+      <c r="V173" s="1" t="inlineStr"/>
+      <c r="W173" s="1" t="inlineStr"/>
+      <c r="X173" s="1" t="inlineStr"/>
+      <c r="Y173" s="1" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr"/>
+      <c r="B174" s="1" t="inlineStr"/>
+      <c r="C174" s="1" t="inlineStr"/>
+      <c r="D174" s="1" t="inlineStr"/>
+      <c r="E174" s="1" t="inlineStr"/>
+      <c r="F174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr"/>
+      <c r="H174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr"/>
+      <c r="J174" s="1" t="inlineStr"/>
+      <c r="K174" s="1" t="inlineStr"/>
+      <c r="L174" s="1" t="inlineStr"/>
+      <c r="M174" s="1" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr">
+        <is>
+          <t>L397: symbol-only separator/garbage line :: 1, 250</t>
+        </is>
+      </c>
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr"/>
+      <c r="R174" s="1" t="inlineStr"/>
+      <c r="S174" s="1" t="inlineStr"/>
+      <c r="T174" s="1" t="inlineStr"/>
+      <c r="U174" s="1" t="inlineStr"/>
+      <c r="V174" s="1" t="inlineStr"/>
+      <c r="W174" s="1" t="inlineStr"/>
+      <c r="X174" s="1" t="inlineStr"/>
+      <c r="Y174" s="1" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr"/>
+      <c r="B175" s="1" t="inlineStr"/>
+      <c r="C175" s="1" t="inlineStr"/>
+      <c r="D175" s="1" t="inlineStr"/>
+      <c r="E175" s="1" t="inlineStr"/>
+      <c r="F175" s="1" t="inlineStr"/>
+      <c r="G175" s="1" t="inlineStr"/>
+      <c r="H175" s="1" t="inlineStr"/>
+      <c r="I175" s="1" t="inlineStr"/>
+      <c r="J175" s="1" t="inlineStr"/>
+      <c r="K175" s="1" t="inlineStr"/>
+      <c r="L175" s="1" t="inlineStr"/>
+      <c r="M175" s="1" t="inlineStr"/>
+      <c r="N175" s="1" t="inlineStr">
+        <is>
+          <t>L432: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="O175" s="1" t="inlineStr"/>
+      <c r="P175" s="1" t="inlineStr"/>
+      <c r="Q175" s="1" t="inlineStr"/>
+      <c r="R175" s="1" t="inlineStr"/>
+      <c r="S175" s="1" t="inlineStr"/>
+      <c r="T175" s="1" t="inlineStr"/>
+      <c r="U175" s="1" t="inlineStr"/>
+      <c r="V175" s="1" t="inlineStr"/>
+      <c r="W175" s="1" t="inlineStr"/>
+      <c r="X175" s="1" t="inlineStr"/>
+      <c r="Y175" s="1" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr"/>
+      <c r="B176" s="1" t="inlineStr"/>
+      <c r="C176" s="1" t="inlineStr"/>
+      <c r="D176" s="1" t="inlineStr"/>
+      <c r="E176" s="1" t="inlineStr"/>
+      <c r="F176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr"/>
+      <c r="H176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr"/>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
+      <c r="L176" s="1" t="inlineStr"/>
+      <c r="M176" s="1" t="inlineStr"/>
+      <c r="N176" s="1" t="inlineStr">
+        <is>
+          <t>L444: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr"/>
+      <c r="R176" s="1" t="inlineStr"/>
+      <c r="S176" s="1" t="inlineStr"/>
+      <c r="T176" s="1" t="inlineStr"/>
+      <c r="U176" s="1" t="inlineStr"/>
+      <c r="V176" s="1" t="inlineStr"/>
+      <c r="W176" s="1" t="inlineStr"/>
+      <c r="X176" s="1" t="inlineStr"/>
+      <c r="Y176" s="1" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr"/>
+      <c r="B177" s="1" t="inlineStr"/>
+      <c r="C177" s="1" t="inlineStr"/>
+      <c r="D177" s="1" t="inlineStr"/>
+      <c r="E177" s="1" t="inlineStr"/>
+      <c r="F177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr"/>
+      <c r="H177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr"/>
+      <c r="J177" s="1" t="inlineStr"/>
+      <c r="K177" s="1" t="inlineStr"/>
+      <c r="L177" s="1" t="inlineStr"/>
+      <c r="M177" s="1" t="inlineStr"/>
+      <c r="N177" s="1" t="inlineStr">
+        <is>
+          <t>L504: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="O177" s="1" t="inlineStr"/>
+      <c r="P177" s="1" t="inlineStr"/>
+      <c r="Q177" s="1" t="inlineStr"/>
+      <c r="R177" s="1" t="inlineStr"/>
+      <c r="S177" s="1" t="inlineStr"/>
+      <c r="T177" s="1" t="inlineStr"/>
+      <c r="U177" s="1" t="inlineStr"/>
+      <c r="V177" s="1" t="inlineStr"/>
+      <c r="W177" s="1" t="inlineStr"/>
+      <c r="X177" s="1" t="inlineStr"/>
+      <c r="Y177" s="1" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr"/>
+      <c r="B178" s="1" t="inlineStr"/>
+      <c r="C178" s="1" t="inlineStr"/>
+      <c r="D178" s="1" t="inlineStr"/>
+      <c r="E178" s="1" t="inlineStr"/>
+      <c r="F178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr"/>
+      <c r="H178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr"/>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
+      <c r="L178" s="1" t="inlineStr"/>
+      <c r="M178" s="1" t="inlineStr"/>
+      <c r="N178" s="1" t="inlineStr">
+        <is>
+          <t>L771: symbol-only separator/garbage line :: $1.50.</t>
+        </is>
+      </c>
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr"/>
+      <c r="R178" s="1" t="inlineStr"/>
+      <c r="S178" s="1" t="inlineStr"/>
+      <c r="T178" s="1" t="inlineStr"/>
+      <c r="U178" s="1" t="inlineStr"/>
+      <c r="V178" s="1" t="inlineStr"/>
+      <c r="W178" s="1" t="inlineStr"/>
+      <c r="X178" s="1" t="inlineStr"/>
+      <c r="Y178" s="1" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr"/>
+      <c r="B179" s="1" t="inlineStr"/>
+      <c r="C179" s="1" t="inlineStr"/>
+      <c r="D179" s="1" t="inlineStr"/>
+      <c r="E179" s="1" t="inlineStr"/>
+      <c r="F179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr"/>
+      <c r="H179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr"/>
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
+      <c r="L179" s="1" t="inlineStr"/>
+      <c r="M179" s="1" t="inlineStr"/>
+      <c r="N179" s="1" t="inlineStr">
+        <is>
+          <t>L853: isolated marker/symbol line :: `</t>
+        </is>
+      </c>
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr"/>
+      <c r="R179" s="1" t="inlineStr"/>
+      <c r="S179" s="1" t="inlineStr"/>
+      <c r="T179" s="1" t="inlineStr"/>
+      <c r="U179" s="1" t="inlineStr"/>
+      <c r="V179" s="1" t="inlineStr"/>
+      <c r="W179" s="1" t="inlineStr"/>
+      <c r="X179" s="1" t="inlineStr"/>
+      <c r="Y179" s="1" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr"/>
+      <c r="B180" s="1" t="inlineStr"/>
+      <c r="C180" s="1" t="inlineStr"/>
+      <c r="D180" s="1" t="inlineStr"/>
+      <c r="E180" s="1" t="inlineStr"/>
+      <c r="F180" s="1" t="inlineStr"/>
+      <c r="G180" s="1" t="inlineStr"/>
+      <c r="H180" s="1" t="inlineStr"/>
+      <c r="I180" s="1" t="inlineStr"/>
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
+      <c r="L180" s="1" t="inlineStr"/>
+      <c r="M180" s="1" t="inlineStr"/>
+      <c r="N180" s="1" t="inlineStr">
+        <is>
+          <t>L900: isolated marker/symbol line :: d</t>
+        </is>
+      </c>
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr"/>
+      <c r="R180" s="1" t="inlineStr"/>
+      <c r="S180" s="1" t="inlineStr"/>
+      <c r="T180" s="1" t="inlineStr"/>
+      <c r="U180" s="1" t="inlineStr"/>
+      <c r="V180" s="1" t="inlineStr"/>
+      <c r="W180" s="1" t="inlineStr"/>
+      <c r="X180" s="1" t="inlineStr"/>
+      <c r="Y180" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
